--- a/data/trans_orig/ED_INF-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/ED_INF-Estudios-trans_orig.xlsx
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,88; 9,4</t>
+          <t>7,82; 9,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,56; 9,13</t>
+          <t>7,51; 9,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,01; 8,99</t>
+          <t>7,14; 9,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,85; 11,59</t>
+          <t>8,81; 11,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,31; 8,84</t>
+          <t>7,29; 8,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,41; 9,02</t>
+          <t>7,43; 9,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,6; 9,27</t>
+          <t>7,63; 9,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,08; 9,97</t>
+          <t>8,1; 10,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,86; 8,96</t>
+          <t>7,78; 8,9</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,7; 8,92</t>
+          <t>7,7; 8,88</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,66; 8,84</t>
+          <t>7,67; 8,93</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,71; 10,48</t>
+          <t>8,67; 10,38</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,54; 8,29</t>
+          <t>7,55; 8,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,89; 7,62</t>
+          <t>6,89; 7,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,45; 8,12</t>
+          <t>7,48; 8,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,25; 10,83</t>
+          <t>9,27; 10,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,58; 8,32</t>
+          <t>7,61; 8,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,99; 7,69</t>
+          <t>6,98; 7,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,4; 8,07</t>
+          <t>7,38; 8,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,33; 10,18</t>
+          <t>9,32; 10,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,7; 8,2</t>
+          <t>7,67; 8,17</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,07; 7,56</t>
+          <t>7,05; 7,53</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,52; 8,0</t>
+          <t>7,52; 8,01</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,41; 10,25</t>
+          <t>9,41; 10,19</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,18; 7,26</t>
+          <t>6,11; 7,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,05; 7,26</t>
+          <t>6,09; 7,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,22; 7,37</t>
+          <t>6,24; 7,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,59; 9,74</t>
+          <t>8,63; 9,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,15; 7,35</t>
+          <t>6,13; 7,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,05; 7,23</t>
+          <t>6,03; 7,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,26; 7,43</t>
+          <t>6,27; 7,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,78; 9,88</t>
+          <t>8,79; 9,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,31; 7,1</t>
+          <t>6,31; 7,15</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,23; 7,04</t>
+          <t>6,22; 7,04</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,38; 7,2</t>
+          <t>6,39; 7,2</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,87; 9,63</t>
+          <t>8,87; 9,64</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,41; 8,01</t>
+          <t>7,41; 7,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,98; 7,57</t>
+          <t>6,99; 7,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,29; 7,86</t>
+          <t>7,29; 7,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,27; 10,29</t>
+          <t>9,24; 10,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,39; 7,97</t>
+          <t>7,42; 7,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,97; 7,55</t>
+          <t>6,96; 7,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,29; 7,84</t>
+          <t>7,29; 7,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,25; 9,9</t>
+          <t>9,24; 9,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,51; 7,9</t>
+          <t>7,5; 7,92</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,08; 7,47</t>
+          <t>7,06; 7,46</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,37; 7,76</t>
+          <t>7,36; 7,77</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,34; 9,96</t>
+          <t>9,36; 9,98</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/ED_INF-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/ED_INF-Estudios-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8,09</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8,24</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8,45</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9,45</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>8,64</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>8,37</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>8,07</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9,92</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8,09</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>8,24</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8,45</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>9,09</t>
+          <t>9,63</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,48</t>
+          <t>9,53</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,82; 9,39</t>
+          <t>7,25; 8,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,51; 9,14</t>
+          <t>7,41; 9,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,14; 9,06</t>
+          <t>7,63; 9,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,81; 11,5</t>
+          <t>8,56; 10,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,29; 8,87</t>
+          <t>7,79; 9,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,43; 9,08</t>
+          <t>7,57; 9,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,63; 9,24</t>
+          <t>7,11; 9,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,1; 10,1</t>
+          <t>8,62; 10,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,78; 8,9</t>
+          <t>7,77; 8,89</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,7; 8,88</t>
+          <t>7,76; 8,88</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,67; 8,93</t>
+          <t>7,68; 8,88</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,67; 10,38</t>
+          <t>8,9; 10,22</t>
         </is>
       </c>
     </row>
@@ -788,44 +788,44 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>7,94</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7,32</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7,73</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9,91</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>7,91</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>7,28</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>7,79</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>9,71</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>7,94</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>7,32</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>7,73</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>9,71</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
           <t>7,93</t>
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,71</t>
+          <t>9,81</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,55; 8,3</t>
+          <t>7,57; 8,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,89; 7,61</t>
+          <t>6,97; 7,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,48; 8,15</t>
+          <t>7,38; 8,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,27; 10,71</t>
+          <t>9,55; 10,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,61; 8,28</t>
+          <t>7,57; 8,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,98; 7,63</t>
+          <t>6,9; 7,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,38; 8,03</t>
+          <t>7,44; 8,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,32; 10,19</t>
+          <t>9,37; 10,04</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,67; 8,17</t>
+          <t>7,67; 8,19</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,05; 7,53</t>
+          <t>7,07; 7,56</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,52; 8,01</t>
+          <t>7,51; 7,99</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,41; 10,19</t>
+          <t>9,56; 10,09</t>
         </is>
       </c>
     </row>
@@ -933,44 +933,44 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>6,61</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6,8</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>9,53</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>6,71</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>6,65</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>6,78</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9,19</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>9,42</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>6,71</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>6,61</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>6,8</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>9,3</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>6,71</t>
-        </is>
-      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
           <t>6,63</t>
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9,25</t>
+          <t>9,48</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,11; 7,27</t>
+          <t>6,14; 7,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,09; 7,26</t>
+          <t>6,06; 7,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,24; 7,39</t>
+          <t>6,27; 7,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,63; 9,73</t>
+          <t>9,07; 10,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,13; 7,34</t>
+          <t>6,12; 7,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,03; 7,2</t>
+          <t>6,03; 7,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,27; 7,33</t>
+          <t>6,15; 7,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,79; 9,8</t>
+          <t>8,85; 9,97</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,31; 7,15</t>
+          <t>6,32; 7,1</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,22; 7,04</t>
+          <t>6,2; 7,06</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,39; 7,2</t>
+          <t>6,38; 7,2</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,87; 9,64</t>
+          <t>9,13; 9,85</t>
         </is>
       </c>
     </row>
@@ -1068,62 +1068,62 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7,69</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7,26</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7,56</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9,78</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>7,7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>7,27</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>7,56</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9,61</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>9,63</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>7,69</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,26</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>7,27</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>7,56</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>9,56</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>7,69</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>7,27</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>7,56</t>
-        </is>
-      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,58</t>
+          <t>9,71</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,41; 7,97</t>
+          <t>7,42; 7,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,99; 7,57</t>
+          <t>6,99; 7,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,29; 7,84</t>
+          <t>7,3; 7,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,24; 10,26</t>
+          <t>9,48; 10,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,42; 7,98</t>
+          <t>7,44; 8,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,96; 7,52</t>
+          <t>6,96; 7,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,29; 7,83</t>
+          <t>7,27; 7,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,24; 9,91</t>
+          <t>9,34; 9,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,5; 7,92</t>
+          <t>7,49; 7,91</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,06; 7,46</t>
+          <t>7,08; 7,47</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,36; 7,77</t>
+          <t>7,35; 7,76</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,36; 9,98</t>
+          <t>9,51; 9,94</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/ED_INF-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/ED_INF-Estudios-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -646,419 +651,271 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>8,09</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>8,24</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>8,45</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9,45</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8,64</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>8,37</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8,07</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9,63</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>8,37</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>8,31</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8,27</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>9,53</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>8.089275975740891</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>8.236423135592601</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>8.448346496895557</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>9.447031107521262</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>8.637398380683775</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>8.372381777277791</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>8.074589542106619</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>9.630238783001735</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>8.36954079782403</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>8.306753809992257</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>8.274952793782179</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>9.529805927082185</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>7,25; 8,88</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>7,41; 9,04</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>7,63; 9,31</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>8,56; 10,38</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>7,79; 9,36</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>7,57; 9,2</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>7,11; 9,03</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>8,62; 10,68</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>7,77; 8,89</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>7,76; 8,88</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>7,68; 8,88</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>8,9; 10,22</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>7.253647554047442</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>7.410145745923671</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>7.631655696846078</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>8.562543546011847</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>7.793542186487044</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>7.569359443582037</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>7.113288986006395</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>8.617747040915056</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>7.768764982499409</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>7.756617030080053</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>7.680131363830376</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>8.897273261586275</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>8.884491944549097</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>9.040855170918984</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>9.313186037366741</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>10.37937354360833</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>9.360743292370962</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>9.204012452976754</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>9.028932827078043</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>10.67805775868215</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>8.886695409819588</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>8.878273905524329</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>8.882037310245384</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>10.22439722086636</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>7,94</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>7,32</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>7,73</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>9,91</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>7,91</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>7,28</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>7,79</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>9,71</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>7,93</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>7,3</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>7,76</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>9,81</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>7,57; 8,27</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>6,97; 7,68</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>7,38; 8,05</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>9,55; 10,34</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>7,57; 8,33</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6,9; 7,6</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,44; 8,12</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>9,37; 10,04</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>7,67; 8,19</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>7,07; 7,56</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>7,51; 7,99</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>9,56; 10,09</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>7.944619784130227</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>7.316267406265839</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>7.726322794987688</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>9.907808852489266</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>7.906490087784632</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>7.277259988137407</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>7.788618635228228</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>9.709600590063442</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>7.926855059315496</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>7.297633863209454</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>7.756937718321212</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>9.813422514032212</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>6,71</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>6,61</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6,8</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9,53</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>6,71</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>6,65</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>6,78</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>9,42</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>6,71</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>6,63</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>6,79</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>9,48</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>7.569495823694383</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>6.96797690585814</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>7.376269399700186</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>9.548225836156815</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>7.566831698227801</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>6.898226680984753</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>7.444259405182292</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>9.365528262036527</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>7.668998993325326</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>7.071673445285661</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>7.507373115777985</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>9.561691668844265</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>6,14; 7,39</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>6,06; 7,19</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>6,27; 7,33</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>9,07; 10,06</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>6,12; 7,29</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>6,03; 7,24</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>6,15; 7,32</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>8,85; 9,97</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>6,32; 7,1</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>6,2; 7,06</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>6,38; 7,2</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>9,13; 9,85</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>8.270886378872218</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>7.684909542143484</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>8.049188920127479</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>10.33817397720976</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>8.329209507057483</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>7.599901487443585</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>8.119854087081054</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>10.03821720996424</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>8.188117423164606</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>7.564078750239907</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>7.988813486026141</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>10.09015925739291</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,137 +923,269 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>7,69</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>7,26</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>7,56</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9,78</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,7</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,27</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,56</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>9,63</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>7,69</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>7,27</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>7,56</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>9,71</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>6.712883071179164</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>6.611639337736198</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>6.804350604456006</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>9.533142795101533</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>6.708325823253384</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>6.647622004049779</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>6.776907528716872</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>9.417146094872031</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>6.710495195120334</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>6.629343282577614</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>6.791192576489812</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>9.478503859856945</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>7,42; 7,96</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>6,99; 7,55</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>7,3; 7,85</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>9,48; 10,1</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>7,44; 8,0</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>6,96; 7,55</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>7,27; 7,87</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>9,34; 9,91</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>7,49; 7,91</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>7,08; 7,47</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>7,35; 7,76</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>9,51; 9,94</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>6.135090928450725</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>6.064945215512342</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>6.268851734512195</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>9.07196328725944</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>6.120081573129873</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>6.025204287182198</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>6.147083243594967</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>8.846961647383784</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>6.320560378662123</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>6.199038459556218</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>6.384844690809681</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>9.127370248255284</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>7.393345186026063</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>7.190656426136116</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>7.333013739970794</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>10.05895048933629</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>7.287065752469253</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>7.243300869192955</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>7.323220315851443</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>9.97048443265464</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>7.09570431861809</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>7.055272785337314</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>7.199298369651841</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>9.848007963461619</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>7.692225289745093</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>7.260418803813516</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>7.560752428861319</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>9.780471477728199</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>7.697767415738436</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>7.271810580812661</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>7.564667708404688</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>9.63399120203505</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>7.694915467085106</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>7.265953357019282</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>7.562655396620261</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>9.711176786690004</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>7.420919290647423</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>6.985382424389779</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>7.296124518993391</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>9.475469669784273</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>7.435603977477592</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>6.960188731507415</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>7.267688705319162</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>9.338435727717783</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>7.491498634476329</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>7.076197323750061</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>7.347803524329539</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>9.512683139903134</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>7.963833003706275</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>7.552771479496012</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>7.850289141082586</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>10.09525800757605</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>8.002345327215043</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>7.554722198807807</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>7.872403767905337</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>9.911223466128195</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>7.911713747687454</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>7.472617337058615</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>7.761344036894315</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>9.939212240313902</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1204,14 +1193,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
